--- a/Statistical Methods for Data Science/skills/skill1/skill1.xlsx
+++ b/Statistical Methods for Data Science/skills/skill1/skill1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joshb\Documents\JOSH\WORK\SSPU\COLLEGE\Statistical Methods for Data Science\skills\skill1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9225BC4-8C2A-4507-B266-F4ED7A726467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931EE039-FD26-492D-8D54-EB29FB4B4282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{CCC4D97B-2F34-4ECD-8E3C-703FF6BC5BCA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CCC4D97B-2F34-4ECD-8E3C-703FF6BC5BCA}"/>
   </bookViews>
   <sheets>
     <sheet name="Online_Shopping" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="76">
   <si>
     <t>Customer</t>
   </si>
@@ -212,9 +212,6 @@
     <t>Tasks:</t>
   </si>
   <si>
-    <t>Find out appropriate measeres on this dataset using Excel functions/formulas.</t>
-  </si>
-  <si>
     <t>Mean</t>
   </si>
   <si>
@@ -255,6 +252,9 @@
   </si>
   <si>
     <t>Netbanking</t>
+  </si>
+  <si>
+    <t>Find out appropriate measures on this dataset using Excel functions/formulas.</t>
   </si>
 </sst>
 </file>
@@ -337,17 +337,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -662,14 +660,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11EAB982-30CA-4149-91D2-41BF1A4BE07B}">
-  <dimension ref="A1:H51"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -680,7 +681,7 @@
     <col min="15" max="15" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -700,7 +701,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -723,7 +724,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -743,10 +744,10 @@
         <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -766,7 +767,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -785,8 +786,24 @@
       <c r="F5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -806,7 +823,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -825,8 +842,32 @@
       <c r="F7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7">
+        <v>36.76</v>
+      </c>
+      <c r="J7" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7">
+        <v>79343.98</v>
+      </c>
+      <c r="L7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M7">
+        <v>5.56</v>
+      </c>
+      <c r="N7" t="s">
+        <v>61</v>
+      </c>
+      <c r="O7">
+        <v>3092.52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -845,8 +886,32 @@
       <c r="F8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8">
+        <v>1.5066004440325849</v>
+      </c>
+      <c r="J8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8">
+        <v>4084.0699668685334</v>
+      </c>
+      <c r="L8" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8">
+        <v>0.3770562671159684</v>
+      </c>
+      <c r="N8" t="s">
+        <v>62</v>
+      </c>
+      <c r="O8">
+        <v>163.97911574343851</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -865,8 +930,32 @@
       <c r="F9" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9">
+        <v>37.5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>63</v>
+      </c>
+      <c r="K9">
+        <v>82301.5</v>
+      </c>
+      <c r="L9" t="s">
+        <v>63</v>
+      </c>
+      <c r="M9">
+        <v>5.5</v>
+      </c>
+      <c r="N9" t="s">
+        <v>63</v>
+      </c>
+      <c r="O9">
+        <v>3132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -885,8 +974,32 @@
       <c r="F10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H10" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10">
+        <v>39</v>
+      </c>
+      <c r="J10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L10" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10">
+        <v>8</v>
+      </c>
+      <c r="N10" t="s">
+        <v>64</v>
+      </c>
+      <c r="O10" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -905,8 +1018,32 @@
       <c r="F11" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H11" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11">
+        <v>10.653273905141043</v>
+      </c>
+      <c r="J11" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11">
+        <v>28878.735684130585</v>
+      </c>
+      <c r="L11" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11">
+        <v>2.666190433665875</v>
+      </c>
+      <c r="N11" t="s">
+        <v>65</v>
+      </c>
+      <c r="O11">
+        <v>1159.5074471515914</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -925,8 +1062,32 @@
       <c r="F12" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12">
+        <v>113.49224489795908</v>
+      </c>
+      <c r="J12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K12">
+        <v>833981374.7138772</v>
+      </c>
+      <c r="L12" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12">
+        <v>7.1085714285714277</v>
+      </c>
+      <c r="N12" t="s">
+        <v>66</v>
+      </c>
+      <c r="O12">
+        <v>1344457.5200000005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -945,8 +1106,32 @@
       <c r="F13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H13" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13">
+        <v>-1.1704173329560237</v>
+      </c>
+      <c r="J13" t="s">
+        <v>67</v>
+      </c>
+      <c r="K13">
+        <v>-1.1374296443799423</v>
+      </c>
+      <c r="L13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M13">
+        <v>-1.0888718266094166</v>
+      </c>
+      <c r="N13" t="s">
+        <v>67</v>
+      </c>
+      <c r="O13">
+        <v>-0.834103042992695</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -965,8 +1150,32 @@
       <c r="F14" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H14" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14">
+        <v>9.2461642640124284E-2</v>
+      </c>
+      <c r="J14" t="s">
+        <v>68</v>
+      </c>
+      <c r="K14">
+        <v>-0.4133961692925564</v>
+      </c>
+      <c r="L14" t="s">
+        <v>68</v>
+      </c>
+      <c r="M14">
+        <v>-0.13679521538307993</v>
+      </c>
+      <c r="N14" t="s">
+        <v>68</v>
+      </c>
+      <c r="O14">
+        <v>-0.40222159889796888</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -985,8 +1194,32 @@
       <c r="F15" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H15" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15">
+        <v>34</v>
+      </c>
+      <c r="J15" t="s">
+        <v>69</v>
+      </c>
+      <c r="K15">
+        <v>92696</v>
+      </c>
+      <c r="L15" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15">
+        <v>9</v>
+      </c>
+      <c r="N15" t="s">
+        <v>69</v>
+      </c>
+      <c r="O15">
+        <v>4386</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1005,8 +1238,32 @@
       <c r="F16" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H16" t="s">
+        <v>70</v>
+      </c>
+      <c r="I16">
+        <v>21</v>
+      </c>
+      <c r="J16" t="s">
+        <v>70</v>
+      </c>
+      <c r="K16">
+        <v>25336</v>
+      </c>
+      <c r="L16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16" t="s">
+        <v>70</v>
+      </c>
+      <c r="O16">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1025,8 +1282,32 @@
       <c r="F17" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H17" t="s">
+        <v>71</v>
+      </c>
+      <c r="I17">
+        <v>55</v>
+      </c>
+      <c r="J17" t="s">
+        <v>71</v>
+      </c>
+      <c r="K17">
+        <v>118032</v>
+      </c>
+      <c r="L17" t="s">
+        <v>71</v>
+      </c>
+      <c r="M17">
+        <v>10</v>
+      </c>
+      <c r="N17" t="s">
+        <v>71</v>
+      </c>
+      <c r="O17">
+        <v>4895</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -1045,8 +1326,32 @@
       <c r="F18" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H18" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18">
+        <v>1838</v>
+      </c>
+      <c r="J18" t="s">
+        <v>72</v>
+      </c>
+      <c r="K18">
+        <v>3967199</v>
+      </c>
+      <c r="L18" t="s">
+        <v>72</v>
+      </c>
+      <c r="M18">
+        <v>278</v>
+      </c>
+      <c r="N18" t="s">
+        <v>72</v>
+      </c>
+      <c r="O18">
+        <v>154626</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -1065,8 +1370,32 @@
       <c r="F19" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H19" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I19" s="5">
+        <v>50</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K19" s="5">
+        <v>50</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="M19" s="5">
+        <v>50</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="O19" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -1086,7 +1415,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -1105,8 +1434,12 @@
       <c r="F21" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -1125,8 +1458,14 @@
       <c r="F22" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H22" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -1145,8 +1484,14 @@
       <c r="F23" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -1165,8 +1510,14 @@
       <c r="F24" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H24" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -1185,8 +1536,14 @@
       <c r="F25" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H25" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I25" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -1206,7 +1563,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -1226,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -1246,7 +1603,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -1266,7 +1623,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -1286,7 +1643,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -1306,7 +1663,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -1708,7 +2065,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="60" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1731,376 +2088,366 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="2"/>
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3" t="s">
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3">
+        <v>36.76</v>
+      </c>
+      <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3">
+        <v>79343.98</v>
+      </c>
+      <c r="E3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3">
+        <v>5.56</v>
+      </c>
+      <c r="G3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3">
+        <v>3092.52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="2">
-        <v>36.76</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B4">
+        <v>1.5066004440325849</v>
+      </c>
+      <c r="C4" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="2">
-        <v>79343.98</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D4">
+        <v>4084.0699668685334</v>
+      </c>
+      <c r="E4" t="s">
         <v>62</v>
       </c>
-      <c r="F3" s="2">
-        <v>5.56</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="F4">
+        <v>0.3770562671159684</v>
+      </c>
+      <c r="G4" t="s">
         <v>62</v>
       </c>
-      <c r="H3" s="2">
-        <v>3092.52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="H4">
+        <v>163.97911574343851</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="2">
-        <v>1.5066004440325849</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B5">
+        <v>37.5</v>
+      </c>
+      <c r="C5" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="2">
-        <v>4084.0699668685334</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="D5">
+        <v>82301.5</v>
+      </c>
+      <c r="E5" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="2">
-        <v>0.3770562671159684</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="F5">
+        <v>5.5</v>
+      </c>
+      <c r="G5" t="s">
         <v>63</v>
       </c>
-      <c r="H4" s="2">
-        <v>163.97911574343851</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="H5">
+        <v>3132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="2">
-        <v>37.5</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B6">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="2">
-        <v>82301.5</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="D6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E6" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="2">
-        <v>3132</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="H6" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="2">
-        <v>39</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="B7">
+        <v>10.653273905141043</v>
+      </c>
+      <c r="C7" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D7">
+        <v>28878.735684130585</v>
+      </c>
+      <c r="E7" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="2">
-        <v>8</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="F7">
+        <v>2.666190433665875</v>
+      </c>
+      <c r="G7" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="H7">
+        <v>1159.5074471515914</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="2">
-        <v>10.653273905141043</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B8">
+        <v>113.49224489795908</v>
+      </c>
+      <c r="C8" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="2">
-        <v>28878.735684130585</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="D8">
+        <v>833981374.7138772</v>
+      </c>
+      <c r="E8" t="s">
         <v>66</v>
       </c>
-      <c r="F7" s="2">
-        <v>2.666190433665875</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="F8">
+        <v>7.1085714285714277</v>
+      </c>
+      <c r="G8" t="s">
         <v>66</v>
       </c>
-      <c r="H7" s="2">
-        <v>1159.5074471515914</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="H8">
+        <v>1344457.5200000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="2">
-        <v>113.49224489795908</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B9">
+        <v>-1.1704173329560237</v>
+      </c>
+      <c r="C9" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="2">
-        <v>833981374.7138772</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="D9">
+        <v>-1.1374296443799423</v>
+      </c>
+      <c r="E9" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="2">
-        <v>7.1085714285714277</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="F9">
+        <v>-1.0888718266094166</v>
+      </c>
+      <c r="G9" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="2">
-        <v>1344457.5200000005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="H9">
+        <v>-0.834103042992695</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="2">
-        <v>-1.1704173329560237</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="B10">
+        <v>9.2461642640124284E-2</v>
+      </c>
+      <c r="C10" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="2">
-        <v>-1.1374296443799423</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="D10">
+        <v>-0.4133961692925564</v>
+      </c>
+      <c r="E10" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="2">
-        <v>-1.0888718266094166</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="F10">
+        <v>-0.13679521538307993</v>
+      </c>
+      <c r="G10" t="s">
         <v>68</v>
       </c>
-      <c r="H9" s="2">
-        <v>-0.834103042992695</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="H10">
+        <v>-0.40222159889796888</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="2">
-        <v>9.2461642640124284E-2</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="B11">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="2">
-        <v>-0.4133961692925564</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="D11">
+        <v>92696</v>
+      </c>
+      <c r="E11" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="2">
-        <v>-0.13679521538307993</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="F11">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s">
         <v>69</v>
       </c>
-      <c r="H10" s="2">
-        <v>-0.40222159889796888</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="H11">
+        <v>4386</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="2">
-        <v>34</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="B12">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="2">
-        <v>92696</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="D12">
+        <v>25336</v>
+      </c>
+      <c r="E12" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="2">
-        <v>9</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
         <v>70</v>
       </c>
-      <c r="H11" s="2">
-        <v>4386</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="H12">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="2">
-        <v>21</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B13">
+        <v>55</v>
+      </c>
+      <c r="C13" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="2">
-        <v>25336</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="D13">
+        <v>118032</v>
+      </c>
+      <c r="E13" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="2">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
         <v>71</v>
       </c>
-      <c r="H12" s="2">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="H13">
+        <v>4895</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="2">
-        <v>55</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="B14">
+        <v>1838</v>
+      </c>
+      <c r="C14" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="2">
-        <v>118032</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="D14">
+        <v>3967199</v>
+      </c>
+      <c r="E14" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="2">
-        <v>10</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="F14">
+        <v>278</v>
+      </c>
+      <c r="G14" t="s">
         <v>72</v>
       </c>
-      <c r="H13" s="2">
-        <v>4895</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="H14">
+        <v>154626</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="2">
-        <v>1838</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="B15" s="5">
+        <v>50</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="2">
-        <v>3967199</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="D15" s="5">
+        <v>50</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F14" s="2">
-        <v>278</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="F15" s="5">
+        <v>50</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="H14" s="2">
-        <v>154626</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="7">
+      <c r="H15" s="5">
         <v>50</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" s="7">
-        <v>50</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" s="7">
-        <v>50</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" s="7">
-        <v>50</v>
-      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="5"/>
+      <c r="B17" s="4"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -2130,10 +2477,10 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" s="6">
+      <c r="A21" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="5">
         <f>COUNTIF(Online_Shopping!F2:F51,"NetBanking")</f>
         <v>14</v>
       </c>
@@ -2149,11 +2496,11 @@
   <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -2219,22 +2566,22 @@
       <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3" t="s">
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3" t="s">
+      <c r="K3" s="2"/>
+      <c r="L3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3" t="s">
+      <c r="M3" s="2"/>
+      <c r="N3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="3"/>
+      <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -2255,14 +2602,6 @@
       <c r="F4" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -2283,21 +2622,21 @@
       <c r="F5" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>62</v>
+      <c r="H5" t="s">
+        <v>61</v>
       </c>
       <c r="I5">
         <f>AVERAGE(B1:B51)</f>
         <v>36.76</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>62</v>
+      <c r="J5" t="s">
+        <v>61</v>
+      </c>
+      <c r="L5" t="s">
+        <v>61</v>
+      </c>
+      <c r="N5" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -2319,17 +2658,17 @@
       <c r="F6" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>63</v>
+      <c r="H6" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" t="s">
+        <v>62</v>
+      </c>
+      <c r="L6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N6" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -2351,17 +2690,17 @@
       <c r="F7" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>64</v>
+      <c r="H7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J7" t="s">
+        <v>63</v>
+      </c>
+      <c r="L7" t="s">
+        <v>63</v>
+      </c>
+      <c r="N7" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -2383,17 +2722,17 @@
       <c r="F8" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>65</v>
+      <c r="H8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" t="s">
+        <v>64</v>
+      </c>
+      <c r="L8" t="s">
+        <v>64</v>
+      </c>
+      <c r="N8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -2415,17 +2754,17 @@
       <c r="F9" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>66</v>
+      <c r="H9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" t="s">
+        <v>65</v>
+      </c>
+      <c r="L9" t="s">
+        <v>65</v>
+      </c>
+      <c r="N9" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -2447,17 +2786,17 @@
       <c r="F10" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>67</v>
+      <c r="H10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" t="s">
+        <v>66</v>
+      </c>
+      <c r="L10" t="s">
+        <v>66</v>
+      </c>
+      <c r="N10" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -2479,17 +2818,17 @@
       <c r="F11" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>68</v>
+      <c r="H11" t="s">
+        <v>67</v>
+      </c>
+      <c r="J11" t="s">
+        <v>67</v>
+      </c>
+      <c r="L11" t="s">
+        <v>67</v>
+      </c>
+      <c r="N11" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -2511,17 +2850,17 @@
       <c r="F12" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>69</v>
+      <c r="H12" t="s">
+        <v>68</v>
+      </c>
+      <c r="J12" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12" t="s">
+        <v>68</v>
+      </c>
+      <c r="N12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -2543,17 +2882,17 @@
       <c r="F13" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>70</v>
+      <c r="H13" t="s">
+        <v>69</v>
+      </c>
+      <c r="J13" t="s">
+        <v>69</v>
+      </c>
+      <c r="L13" t="s">
+        <v>69</v>
+      </c>
+      <c r="N13" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -2575,17 +2914,17 @@
       <c r="F14" t="s">
         <v>12</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>71</v>
+      <c r="H14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J14" t="s">
+        <v>70</v>
+      </c>
+      <c r="L14" t="s">
+        <v>70</v>
+      </c>
+      <c r="N14" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -2607,17 +2946,17 @@
       <c r="F15" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>72</v>
+      <c r="H15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J15" t="s">
+        <v>71</v>
+      </c>
+      <c r="L15" t="s">
+        <v>71</v>
+      </c>
+      <c r="N15" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -2639,17 +2978,17 @@
       <c r="F16" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>73</v>
+      <c r="H16" t="s">
+        <v>72</v>
+      </c>
+      <c r="J16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L16" t="s">
+        <v>72</v>
+      </c>
+      <c r="N16" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
@@ -2671,22 +3010,22 @@
       <c r="F17" t="s">
         <v>12</v>
       </c>
-      <c r="H17" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I17" s="6"/>
-      <c r="J17" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="K17" s="6"/>
-      <c r="L17" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="M17" s="6"/>
-      <c r="N17" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="O17" s="6"/>
+      <c r="H17" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="O17" s="5"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -2727,10 +3066,10 @@
       <c r="F19" t="s">
         <v>7</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I19" s="5"/>
+      <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -2832,10 +3171,10 @@
       <c r="F23" t="s">
         <v>12</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="I23" s="6">
+      <c r="H23" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I23" s="5">
         <f>COUNTIF(F2:F51,"NetBanking")</f>
         <v>14</v>
       </c>
@@ -3402,5 +3741,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>